--- a/public/forms/OOO_RuntimePlan.xlsx
+++ b/public/forms/OOO_RuntimePlan.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20382"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melephant\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\민원4\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A3AA57-5898-435B-BC28-ADBF0285D03A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B1160D-A10E-425E-A302-9DE37E5F25A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{8ABF4B1D-5BC9-42F2-ACF5-909D4BBB9E92}"/>
+    <workbookView xWindow="2340" yWindow="1035" windowWidth="20355" windowHeight="12465" xr2:uid="{8ABF4B1D-5BC9-42F2-ACF5-909D4BBB9E92}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>학생</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -113,6 +113,18 @@
   <si>
     <t>==&gt; 0: 일, 1: 월, 2: 화, 3: 수, 4:목, 5: 금, 6: 토</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태</t>
+  </si>
+  <si>
+    <t>시간</t>
+  </si>
+  <si>
+    <t>분</t>
+  </si>
+  <si>
+    <t>순서</t>
   </si>
 </sst>
 </file>
@@ -230,7 +242,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -246,7 +258,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -623,16 +635,20 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
+      <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
@@ -675,6 +691,9 @@
         <v>8</v>
       </c>
       <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>1</v>
       </c>
     </row>
@@ -686,6 +705,9 @@
         <v>12</v>
       </c>
       <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
         <v>2</v>
       </c>
     </row>
@@ -697,6 +719,9 @@
         <v>13</v>
       </c>
       <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
         <v>3</v>
       </c>
     </row>
@@ -708,9 +733,11 @@
         <v>18</v>
       </c>
       <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6">
         <v>4</v>
       </c>
-      <c r="D16" s="6"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -720,9 +747,11 @@
         <v>19</v>
       </c>
       <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6">
         <v>5</v>
       </c>
-      <c r="D17" s="6"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
@@ -732,6 +761,9 @@
         <v>1</v>
       </c>
       <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
         <v>6</v>
       </c>
     </row>

--- a/public/forms/OOO_RuntimePlan.xlsx
+++ b/public/forms/OOO_RuntimePlan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\민원4\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B1160D-A10E-425E-A302-9DE37E5F25A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D1BE21-BE87-4B6A-8571-D2B59CFD285D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1035" windowWidth="20355" windowHeight="12465" xr2:uid="{8ABF4B1D-5BC9-42F2-ACF5-909D4BBB9E92}"/>
+    <workbookView xWindow="270" yWindow="150" windowWidth="20355" windowHeight="12465" xr2:uid="{8ABF4B1D-5BC9-42F2-ACF5-909D4BBB9E92}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>학생</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -111,10 +111,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>==&gt; 0: 일, 1: 월, 2: 화, 3: 수, 4:목, 5: 금, 6: 토</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>상태</t>
   </si>
   <si>
@@ -125,6 +121,27 @@
   </si>
   <si>
     <t>순서</t>
+  </si>
+  <si>
+    <t>입실</t>
+  </si>
+  <si>
+    <t>석식</t>
+  </si>
+  <si>
+    <t>퇴실</t>
+  </si>
+  <si>
+    <t>일요일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화요일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>==&gt;일~토요일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -554,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41B3B65D-4A8A-4A38-BA06-796CDFD70E5F}">
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -639,16 +656,16 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
@@ -657,11 +674,11 @@
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
-        <v>0</v>
+      <c r="A12" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -685,85 +702,93 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>3</v>
+      <c r="A14" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="B14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>2</v>
+      <c r="A15" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="B15">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
+        <v>23</v>
+      </c>
+      <c r="C16">
+        <v>40</v>
+      </c>
+      <c r="D16">
         <v>4</v>
       </c>
-      <c r="B16">
-        <v>18</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16" s="6">
-        <v>4</v>
-      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17">
-        <v>19</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17" s="6">
-        <v>5</v>
-      </c>
+      <c r="A17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>5</v>
+      <c r="A18" t="s">
+        <v>25</v>
       </c>
       <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
         <v>1</v>
       </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
       <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>51</v>
+      </c>
+      <c r="D19">
         <v>6</v>
       </c>
     </row>

--- a/public/forms/OOO_RuntimePlan.xlsx
+++ b/public/forms/OOO_RuntimePlan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20390"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\민원4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TTOKSSAEM\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D1BE21-BE87-4B6A-8571-D2B59CFD285D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617065C7-ED14-45BD-B4E3-FFCB48056F3B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="150" windowWidth="20355" windowHeight="12465" xr2:uid="{8ABF4B1D-5BC9-42F2-ACF5-909D4BBB9E92}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{8ABF4B1D-5BC9-42F2-ACF5-909D4BBB9E92}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>학생</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -126,21 +126,27 @@
     <t>입실</t>
   </si>
   <si>
+    <t>일요일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>==&gt;일~토요일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>입실</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>석식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>퇴실</t>
-  </si>
-  <si>
-    <t>일요일</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>화요일</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>==&gt;일~토요일</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -571,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41B3B65D-4A8A-4A38-BA06-796CDFD70E5F}">
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -675,10 +681,10 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -705,10 +711,10 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -716,13 +722,13 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -730,13 +736,13 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B15">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -744,10 +750,10 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B16">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C16">
         <v>40</v>
@@ -758,37 +764,29 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="B17" s="5">
+        <v>18</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B18">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>51</v>
-      </c>
-      <c r="D19">
         <v>6</v>
       </c>
     </row>

--- a/public/forms/OOO_RuntimePlan.xlsx
+++ b/public/forms/OOO_RuntimePlan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20390"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20393"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TTOKSSAEM\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCom\bigint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617065C7-ED14-45BD-B4E3-FFCB48056F3B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EF6EB2-1FF9-490D-8717-5E6949BE35F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{8ABF4B1D-5BC9-42F2-ACF5-909D4BBB9E92}"/>
   </bookViews>
@@ -265,7 +265,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -725,10 +725,10 @@
         <v>28</v>
       </c>
       <c r="B14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -756,7 +756,7 @@
         <v>16</v>
       </c>
       <c r="C16">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D16">
         <v>4</v>
